--- a/artfynd/S 3187-2024 artfynd.xlsx
+++ b/artfynd/S 3187-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -994,48 +994,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128163276</v>
+        <v>137100658</v>
       </c>
       <c r="B5" t="n">
-        <v>93273</v>
+        <v>92389</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>788</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Broddtorpet, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538386</v>
+        <v>538505</v>
       </c>
       <c r="R5" t="n">
-        <v>6681824</v>
+        <v>6681925</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1062,12 +1059,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,7 +1073,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1094,51 +1090,54 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128163276</t>
+          <t>https://artportalen.se/Sighting/137100658</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128162534</v>
+        <v>128163276</v>
       </c>
       <c r="B6" t="n">
-        <v>92632</v>
+        <v>93273</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>788</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Broddtorpet, Broddtorpet, Dlr</t>
+          <t>Broddtorpet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>538515</v>
+        <v>538386</v>
       </c>
       <c r="R6" t="n">
-        <v>6681950</v>
+        <v>6681824</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1179,6 +1178,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1196,16 +1196,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128162534</t>
+          <t>https://artportalen.se/Sighting/128163276</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128164760</v>
+        <v>137100719</v>
       </c>
       <c r="B7" t="n">
-        <v>93215</v>
+        <v>92118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1213,21 +1213,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4368</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1237,10 +1237,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>538503</v>
+        <v>538516</v>
       </c>
       <c r="R7" t="n">
-        <v>6681906</v>
+        <v>6681913</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1298,51 +1298,51 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128164760</t>
+          <t>https://artportalen.se/Sighting/137100719</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127780264</v>
+        <v>137100665</v>
       </c>
       <c r="B8" t="n">
-        <v>92869</v>
+        <v>92550</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Broddtorpet, Broddtorpet, Dlr</t>
+          <t>Broddtorpet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>538514</v>
+        <v>538516</v>
       </c>
       <c r="R8" t="n">
-        <v>6681889</v>
+        <v>6681930</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1400,16 +1400,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127780264</t>
+          <t>https://artportalen.se/Sighting/137100665</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128162107</v>
+        <v>128162534</v>
       </c>
       <c r="B9" t="n">
-        <v>92869</v>
+        <v>92632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1417,21 +1417,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>538496</v>
+        <v>538515</v>
       </c>
       <c r="R9" t="n">
-        <v>6681896</v>
+        <v>6681950</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1502,44 +1502,41 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128162107</t>
+          <t>https://artportalen.se/Sighting/128162534</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127785428</v>
+        <v>128164760</v>
       </c>
       <c r="B10" t="n">
-        <v>87291</v>
+        <v>93215</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>248955</v>
+        <v>4368</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Broddtorpet, Dlr</t>
@@ -1576,12 +1573,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1590,7 +1587,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1607,6 +1603,316 @@
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128164760</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127780264</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Broddtorpet, Broddtorpet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>538514</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6681889</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127780264</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128162107</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Broddtorpet, Broddtorpet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>538496</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6681896</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128162107</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127785428</v>
+      </c>
+      <c r="B13" t="n">
+        <v>87291</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>248955</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tvillingspindling</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cortinarius metarius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Broddtorpet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>538503</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6681906</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/127785428</t>
         </is>
@@ -1623,6 +1929,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3187-2024 artfynd.xlsx
+++ b/artfynd/S 3187-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>137100658</v>
       </c>
       <c r="B5" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>137100719</v>
       </c>
       <c r="B7" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>137100665</v>
       </c>
       <c r="B8" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 3187-2024 artfynd.xlsx
+++ b/artfynd/S 3187-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>137100658</v>
       </c>
       <c r="B5" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>137100719</v>
       </c>
       <c r="B7" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>137100665</v>
       </c>
       <c r="B8" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 3187-2024 artfynd.xlsx
+++ b/artfynd/S 3187-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>137100658</v>
       </c>
       <c r="B5" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>137100719</v>
       </c>
       <c r="B7" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>137100665</v>
       </c>
       <c r="B8" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 3187-2024 artfynd.xlsx
+++ b/artfynd/S 3187-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>137100658</v>
       </c>
       <c r="B5" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>137100719</v>
       </c>
       <c r="B7" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>137100665</v>
       </c>
       <c r="B8" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 3187-2024 artfynd.xlsx
+++ b/artfynd/S 3187-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>137100658</v>
       </c>
       <c r="B5" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>137100719</v>
       </c>
       <c r="B7" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>137100665</v>
       </c>
       <c r="B8" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 3187-2024 artfynd.xlsx
+++ b/artfynd/S 3187-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>137100658</v>
       </c>
       <c r="B5" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>137100719</v>
       </c>
       <c r="B7" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>137100665</v>
       </c>
       <c r="B8" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 3187-2024 artfynd.xlsx
+++ b/artfynd/S 3187-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>137100658</v>
       </c>
       <c r="B5" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>137100719</v>
       </c>
       <c r="B7" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>137100665</v>
       </c>
       <c r="B8" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 3187-2024 artfynd.xlsx
+++ b/artfynd/S 3187-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>137100658</v>
       </c>
       <c r="B5" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>137100719</v>
       </c>
       <c r="B7" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>137100665</v>
       </c>
       <c r="B8" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 3187-2024 artfynd.xlsx
+++ b/artfynd/S 3187-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>137100658</v>
       </c>
       <c r="B5" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>137100719</v>
       </c>
       <c r="B7" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>137100665</v>
       </c>
       <c r="B8" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 3187-2024 artfynd.xlsx
+++ b/artfynd/S 3187-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>137100658</v>
       </c>
       <c r="B5" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>137100719</v>
       </c>
       <c r="B7" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>137100665</v>
       </c>
       <c r="B8" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 3187-2024 artfynd.xlsx
+++ b/artfynd/S 3187-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>137100658</v>
       </c>
       <c r="B5" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>137100719</v>
       </c>
       <c r="B7" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>137100665</v>
       </c>
       <c r="B8" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 3187-2024 artfynd.xlsx
+++ b/artfynd/S 3187-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>137100658</v>
       </c>
       <c r="B5" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>137100719</v>
       </c>
       <c r="B7" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>137100665</v>
       </c>
       <c r="B8" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 3187-2024 artfynd.xlsx
+++ b/artfynd/S 3187-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>137100658</v>
       </c>
       <c r="B5" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>137100719</v>
       </c>
       <c r="B7" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>137100665</v>
       </c>
       <c r="B8" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 3187-2024 artfynd.xlsx
+++ b/artfynd/S 3187-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>137100658</v>
       </c>
       <c r="B5" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>137100719</v>
       </c>
       <c r="B7" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>137100665</v>
       </c>
       <c r="B8" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 3187-2024 artfynd.xlsx
+++ b/artfynd/S 3187-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>137100658</v>
       </c>
       <c r="B5" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>137100719</v>
       </c>
       <c r="B7" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>137100665</v>
       </c>
       <c r="B8" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
